--- a/Labor Mapping.xlsx
+++ b/Labor Mapping.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc6e612a83a384d3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdb5c1ae2cbcd4770"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1896,7 +1896,7 @@
         <x:v>82190</x:v>
       </x:c>
       <x:c r="C57" s="6" t="n">
-        <x:v>82210</x:v>
+        <x:v>82220</x:v>
       </x:c>
       <x:c r="D57" s="6" t="n">
         <x:v>39000091</x:v>
